--- a/01_Raw_data/RC log.xlsx
+++ b/01_Raw_data/RC log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83FE6C6-A56B-43BF-8B3B-DD4A2F6460CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71870B2-B66D-4B38-8E47-642B227FC755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{A079E74B-2391-4069-81A1-6515CCD90540}"/>
+    <workbookView xWindow="-28920" yWindow="2220" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A079E74B-2391-4069-81A1-6515CCD90540}"/>
   </bookViews>
   <sheets>
     <sheet name="RC log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>surface_elevation_m</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -11010,7 +11013,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C17" si="0">CONVERT(B3,"ft","m")</f>
+        <f t="shared" ref="C3:C16" si="0">CONVERT(B3,"ft","m")</f>
         <v>2.1335999999999999</v>
       </c>
       <c r="D3">
@@ -11020,7 +11023,7 @@
         <v>0.42</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H66" si="1">D3-F3</f>
+        <f t="shared" ref="H3:H19" si="1">D3-F3</f>
         <v>1.6800000000000002</v>
       </c>
       <c r="I3">
@@ -11438,8 +11441,7 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D17">
         <v>2.25</v>
@@ -11494,6 +11496,9 @@
       <c r="A19" t="s">
         <v>37</v>
       </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
       <c r="D19">
         <v>0.02</v>
       </c>
@@ -11512,8 +11517,16 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
       <c r="H20">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20">
@@ -11524,8 +11537,16 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
       <c r="H21">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21">
@@ -11536,8 +11557,16 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="H22">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22">
@@ -11548,10 +11577,6 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J23">
         <v>638.25340000000006</v>
       </c>
@@ -11560,10 +11585,6 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J24">
         <v>623.13530000000003</v>
       </c>
@@ -11572,10 +11593,6 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J25">
         <v>607.76750000000004</v>
       </c>
@@ -11584,10 +11601,6 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J26">
         <v>592.50710000000004</v>
       </c>
@@ -11596,9 +11609,8 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H27">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="E27" t="s">
+        <v>58</v>
       </c>
       <c r="J27">
         <v>577.47490000000005</v>
@@ -11608,10 +11620,6 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J28">
         <v>562.39620000000002</v>
       </c>
@@ -11620,10 +11628,6 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J29">
         <v>562.76610000000005</v>
       </c>
@@ -11632,10 +11636,6 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J30">
         <v>562.50009999999997</v>
       </c>
@@ -11644,10 +11644,6 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J31">
         <v>562.36329999999998</v>
       </c>
@@ -11656,10 +11652,6 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.75">
-      <c r="H32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="J32">
         <v>577.42870000000005</v>
       </c>
@@ -11667,11 +11659,7 @@
         <v>66.438630000000003</v>
       </c>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="33" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J33">
         <v>577.51340000000005</v>
       </c>
@@ -11679,11 +11667,7 @@
         <v>66.721999999999994</v>
       </c>
     </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="34" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J34">
         <v>622.80349999999999</v>
       </c>
@@ -11691,11 +11675,7 @@
         <v>66.502319999999997</v>
       </c>
     </row>
-    <row r="35" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="35" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J35">
         <v>698.44579999999996</v>
       </c>
@@ -11703,11 +11683,7 @@
         <v>66.603359999999995</v>
       </c>
     </row>
-    <row r="36" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="36" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J36">
         <v>728.82050000000004</v>
       </c>
@@ -11715,11 +11691,7 @@
         <v>66.735640000000004</v>
       </c>
     </row>
-    <row r="37" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="37" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J37">
         <v>744.46180000000004</v>
       </c>
@@ -11727,11 +11699,7 @@
         <v>67.009540000000001</v>
       </c>
     </row>
-    <row r="38" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H38">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="38" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J38">
         <v>728.54539999999997</v>
       </c>
@@ -11739,11 +11707,7 @@
         <v>66.730959999999996</v>
       </c>
     </row>
-    <row r="39" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H39">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="39" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J39">
         <v>728.59079999999994</v>
       </c>
@@ -11751,11 +11715,7 @@
         <v>66.700519999999997</v>
       </c>
     </row>
-    <row r="40" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="40" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J40">
         <v>728.52480000000003</v>
       </c>
@@ -11763,11 +11723,7 @@
         <v>66.432400000000001</v>
       </c>
     </row>
-    <row r="41" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H41">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="41" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J41">
         <v>744.04729999999995</v>
       </c>
@@ -11775,11 +11731,7 @@
         <v>66.440209999999993</v>
       </c>
     </row>
-    <row r="42" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="42" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J42">
         <v>744.07650000000001</v>
       </c>
@@ -11787,11 +11739,7 @@
         <v>66.810680000000005</v>
       </c>
     </row>
-    <row r="43" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="43" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J43">
         <v>759.36440000000005</v>
       </c>
@@ -11799,11 +11747,7 @@
         <v>66.765969999999996</v>
       </c>
     </row>
-    <row r="44" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="44" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J44">
         <v>774.61670000000004</v>
       </c>
@@ -11811,11 +11755,7 @@
         <v>66.688059999999993</v>
       </c>
     </row>
-    <row r="45" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="45" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J45">
         <v>774.67240000000004</v>
       </c>
@@ -11823,11 +11763,7 @@
         <v>66.708640000000003</v>
       </c>
     </row>
-    <row r="46" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="46" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J46">
         <v>789.6807</v>
       </c>
@@ -11835,11 +11771,7 @@
         <v>66.707120000000003</v>
       </c>
     </row>
-    <row r="47" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="47" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J47">
         <v>834.55520000000001</v>
       </c>
@@ -11847,11 +11779,7 @@
         <v>66.699510000000004</v>
       </c>
     </row>
-    <row r="48" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="48" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J48">
         <v>834.96130000000005</v>
       </c>
@@ -11859,11 +11787,7 @@
         <v>67.011229999999998</v>
       </c>
     </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H49">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J49">
         <v>850.197</v>
       </c>
@@ -11871,11 +11795,7 @@
         <v>66.578879999999998</v>
       </c>
     </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J50">
         <v>865.02120000000002</v>
       </c>
@@ -11883,11 +11803,7 @@
         <v>66.439570000000003</v>
       </c>
     </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J51">
         <v>865.25400000000002</v>
       </c>
@@ -11895,11 +11811,7 @@
         <v>66.421679999999995</v>
       </c>
     </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J52">
         <v>880.46839999999997</v>
       </c>
@@ -11907,11 +11819,7 @@
         <v>66.699039999999997</v>
       </c>
     </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J53">
         <v>895.39089999999999</v>
       </c>
@@ -11919,11 +11827,7 @@
         <v>66.41798</v>
       </c>
     </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H54">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J54">
         <v>895.33799999999997</v>
       </c>
@@ -11931,11 +11835,7 @@
         <v>66.555769999999995</v>
       </c>
     </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="55" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J55">
         <v>910.66690000000006</v>
       </c>
@@ -11943,11 +11843,7 @@
         <v>66.713909999999998</v>
       </c>
     </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H56">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="56" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J56">
         <v>925.98109999999997</v>
       </c>
@@ -11955,11 +11851,7 @@
         <v>66.679460000000006</v>
       </c>
     </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H57">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="57" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J57">
         <v>940.77919999999995</v>
       </c>
@@ -11967,11 +11859,7 @@
         <v>66.716350000000006</v>
       </c>
     </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H58">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="58" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J58">
         <v>955.72770000000003</v>
       </c>
@@ -11979,11 +11867,7 @@
         <v>66.600700000000003</v>
       </c>
     </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H59">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="59" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J59">
         <v>970.87699999999995</v>
       </c>
@@ -11991,11 +11875,7 @@
         <v>67.232489999999999</v>
       </c>
     </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H60">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="60" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J60">
         <v>986.60170000000005</v>
       </c>
@@ -12003,11 +11883,7 @@
         <v>66.475719999999995</v>
       </c>
     </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="61" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J61">
         <v>1001.513</v>
       </c>
@@ -12015,11 +11891,7 @@
         <v>69.48903</v>
       </c>
     </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H62">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="62" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J62">
         <v>1016.558</v>
       </c>
@@ -12027,11 +11899,7 @@
         <v>66.661689999999993</v>
       </c>
     </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H63">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="63" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J63">
         <v>1031.5419999999999</v>
       </c>
@@ -12039,11 +11907,7 @@
         <v>77.511840000000007</v>
       </c>
     </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="64" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J64">
         <v>1047.2439999999999</v>
       </c>
@@ -12051,11 +11915,7 @@
         <v>66.713200000000001</v>
       </c>
     </row>
-    <row r="65" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="65" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J65">
         <v>1061.7260000000001</v>
       </c>
@@ -12063,11 +11923,7 @@
         <v>80.544539999999998</v>
       </c>
     </row>
-    <row r="66" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H66">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="66" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J66">
         <v>1077.3230000000001</v>
       </c>
@@ -12075,11 +11931,7 @@
         <v>66.882890000000003</v>
       </c>
     </row>
-    <row r="67" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H67">
-        <f t="shared" ref="H67:H130" si="2">D67-F67</f>
-        <v>0</v>
-      </c>
+    <row r="67" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J67">
         <v>1107.306</v>
       </c>
@@ -12087,11 +11939,7 @@
         <v>82.613020000000006</v>
       </c>
     </row>
-    <row r="68" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H68">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="68" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J68">
         <v>1122.7550000000001</v>
       </c>
@@ -12099,11 +11947,7 @@
         <v>66.875720000000001</v>
       </c>
     </row>
-    <row r="69" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H69">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="69" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J69">
         <v>1167.7729999999999</v>
       </c>
@@ -12111,11 +11955,7 @@
         <v>81.679119999999998</v>
       </c>
     </row>
-    <row r="70" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="70" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J70">
         <v>1183.0219999999999</v>
       </c>
@@ -12123,11 +11963,7 @@
         <v>76.520039999999995</v>
       </c>
     </row>
-    <row r="71" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H71">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="71" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J71">
         <v>1183.3119999999999</v>
       </c>
@@ -12135,11 +11971,7 @@
         <v>76.523030000000006</v>
       </c>
     </row>
-    <row r="72" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H72">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="72" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J72">
         <v>1198.4190000000001</v>
       </c>
@@ -12147,11 +11979,7 @@
         <v>76.558539999999994</v>
       </c>
     </row>
-    <row r="73" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="73" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J73">
         <v>1213.2</v>
       </c>
@@ -12159,11 +11987,7 @@
         <v>76.322270000000003</v>
       </c>
     </row>
-    <row r="74" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H74">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="74" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J74">
         <v>1213.443</v>
       </c>
@@ -12171,11 +11995,7 @@
         <v>76.840400000000002</v>
       </c>
     </row>
-    <row r="75" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="75" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J75">
         <v>1228.8979999999999</v>
       </c>
@@ -12183,11 +12003,7 @@
         <v>76.866280000000003</v>
       </c>
     </row>
-    <row r="76" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="76" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J76">
         <v>1244.1220000000001</v>
       </c>
@@ -12195,11 +12011,7 @@
         <v>76.297600000000003</v>
       </c>
     </row>
-    <row r="77" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H77">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="77" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J77">
         <v>1259.123</v>
       </c>
@@ -12207,11 +12019,7 @@
         <v>76.881839999999997</v>
       </c>
     </row>
-    <row r="78" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H78">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="78" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J78">
         <v>1258.752</v>
       </c>
@@ -12219,11 +12027,7 @@
         <v>76.468999999999994</v>
       </c>
     </row>
-    <row r="79" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="79" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J79">
         <v>1304.1369999999999</v>
       </c>
@@ -12231,11 +12035,7 @@
         <v>76.618129999999994</v>
       </c>
     </row>
-    <row r="80" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H80">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="80" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J80">
         <v>1349.9849999999999</v>
       </c>
@@ -12243,11 +12043,7 @@
         <v>76.480620000000002</v>
       </c>
     </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H81">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="81" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J81">
         <v>1350.0229999999999</v>
       </c>
@@ -12255,11 +12051,7 @@
         <v>76.648570000000007</v>
       </c>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H82">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="82" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J82">
         <v>1364.8150000000001</v>
       </c>
@@ -12267,11 +12059,7 @@
         <v>76.311499999999995</v>
       </c>
     </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H83">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="83" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J83">
         <v>1380.152</v>
       </c>
@@ -12279,11 +12067,7 @@
         <v>76.679150000000007</v>
       </c>
     </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H84">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="84" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J84">
         <v>1380.086</v>
       </c>
@@ -12291,11 +12075,7 @@
         <v>76.621639999999999</v>
       </c>
     </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H85">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="85" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J85">
         <v>1379.7149999999999</v>
       </c>
@@ -12303,11 +12083,7 @@
         <v>76.371279999999999</v>
       </c>
     </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H86">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="86" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J86">
         <v>1394.9970000000001</v>
       </c>
@@ -12315,11 +12091,7 @@
         <v>76.636949999999999</v>
       </c>
     </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H87">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="87" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J87">
         <v>1410.3409999999999</v>
       </c>
@@ -12327,11 +12099,7 @@
         <v>76.882059999999996</v>
       </c>
     </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H88">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="88" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J88">
         <v>1425.6030000000001</v>
       </c>
@@ -12339,11 +12107,7 @@
         <v>76.91395</v>
       </c>
     </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H89">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="89" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J89">
         <v>1409.979</v>
       </c>
@@ -12351,11 +12115,7 @@
         <v>76.394909999999996</v>
       </c>
     </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H90">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="90" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J90">
         <v>1410.248</v>
       </c>
@@ -12363,11 +12123,7 @@
         <v>76.664580000000001</v>
       </c>
     </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H91">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="91" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J91">
         <v>1455.58</v>
       </c>
@@ -12375,11 +12131,7 @@
         <v>76.792010000000005</v>
       </c>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H92">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="92" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J92">
         <v>1486.2159999999999</v>
       </c>
@@ -12387,11 +12139,7 @@
         <v>86.622889999999998</v>
       </c>
     </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H93">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="93" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J93">
         <v>1485.806</v>
       </c>
@@ -12399,11 +12147,7 @@
         <v>86.426929999999999</v>
       </c>
     </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H94">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="94" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J94">
         <v>1516.0709999999999</v>
       </c>
@@ -12411,11 +12155,7 @@
         <v>86.291049999999998</v>
       </c>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H95">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="95" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J95">
         <v>1515.9280000000001</v>
       </c>
@@ -12423,11 +12163,7 @@
         <v>86.616039999999998</v>
       </c>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H96">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="96" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J96">
         <v>1516.348</v>
       </c>
@@ -12435,11 +12171,7 @@
         <v>86.725769999999997</v>
       </c>
     </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H97">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="97" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J97">
         <v>1531.32</v>
       </c>
@@ -12447,11 +12179,7 @@
         <v>86.364840000000001</v>
       </c>
     </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H98">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="98" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J98">
         <v>1531.4570000000001</v>
       </c>
@@ -12459,11 +12187,7 @@
         <v>86.454610000000002</v>
       </c>
     </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H99">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="99" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J99">
         <v>1531.6220000000001</v>
       </c>
@@ -12471,11 +12195,7 @@
         <v>86.403989999999993</v>
       </c>
     </row>
-    <row r="100" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H100">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="100" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J100">
         <v>1531.232</v>
       </c>
@@ -12483,11 +12203,7 @@
         <v>86.471239999999995</v>
       </c>
     </row>
-    <row r="101" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H101">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="101" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J101">
         <v>1531.4369999999999</v>
       </c>
@@ -12495,11 +12211,7 @@
         <v>86.733379999999997</v>
       </c>
     </row>
-    <row r="102" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H102">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="102" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J102">
         <v>1531.0519999999999</v>
       </c>
@@ -12507,11 +12219,7 @@
         <v>86.402079999999998</v>
       </c>
     </row>
-    <row r="103" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H103">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="103" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J103">
         <v>1531.268</v>
       </c>
@@ -12519,11 +12227,7 @@
         <v>86.439710000000005</v>
       </c>
     </row>
-    <row r="104" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H104">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="104" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J104">
         <v>1546.579</v>
       </c>
@@ -12531,11 +12235,7 @@
         <v>86.730919999999998</v>
       </c>
     </row>
-    <row r="105" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H105">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="105" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J105">
         <v>1546.319</v>
       </c>
@@ -12543,11 +12243,7 @@
         <v>86.136409999999998</v>
       </c>
     </row>
-    <row r="106" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H106">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="106" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J106">
         <v>1576.8009999999999</v>
       </c>
@@ -12555,11 +12251,7 @@
         <v>86.486429999999999</v>
       </c>
     </row>
-    <row r="107" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H107">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="107" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J107">
         <v>1591.886</v>
       </c>
@@ -12567,11 +12259,7 @@
         <v>86.408940000000001</v>
       </c>
     </row>
-    <row r="108" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H108">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="108" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J108">
         <v>1607.3309999999999</v>
       </c>
@@ -12579,11 +12267,7 @@
         <v>86.266360000000006</v>
       </c>
     </row>
-    <row r="109" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H109">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="109" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J109">
         <v>1607.1669999999999</v>
       </c>
@@ -12591,11 +12275,7 @@
         <v>96.321259999999995</v>
       </c>
     </row>
-    <row r="110" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H110">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="110" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J110">
         <v>1622.027</v>
       </c>
@@ -12603,11 +12283,7 @@
         <v>95.994619999999998</v>
       </c>
     </row>
-    <row r="111" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H111">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="111" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J111">
         <v>1622.26</v>
       </c>
@@ -12615,11 +12291,7 @@
         <v>96.47484</v>
       </c>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H112">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="112" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J112">
         <v>1637.01</v>
       </c>
@@ -12627,11 +12299,7 @@
         <v>96.487459999999999</v>
       </c>
     </row>
-    <row r="113" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H113">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="113" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J113">
         <v>1637.1120000000001</v>
       </c>
@@ -12639,11 +12307,7 @@
         <v>95.942539999999994</v>
       </c>
     </row>
-    <row r="114" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H114">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="114" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J114">
         <v>1652.441</v>
       </c>
@@ -12651,11 +12315,7 @@
         <v>96.212249999999997</v>
       </c>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="115" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J115">
         <v>1652.6880000000001</v>
       </c>
@@ -12663,11 +12323,7 @@
         <v>96.16</v>
       </c>
     </row>
-    <row r="116" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H116">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="116" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J116">
         <v>1652.4690000000001</v>
       </c>
@@ -12675,11 +12331,7 @@
         <v>96.532060000000001</v>
       </c>
     </row>
-    <row r="117" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H117">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="117" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J117">
         <v>1667.163</v>
       </c>
@@ -12687,11 +12339,7 @@
         <v>96.261859999999999</v>
       </c>
     </row>
-    <row r="118" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H118">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="118" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J118">
         <v>1682.24</v>
       </c>
@@ -12699,11 +12347,7 @@
         <v>96.204570000000004</v>
       </c>
     </row>
-    <row r="119" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H119">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="119" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J119">
         <v>1682.7049999999999</v>
       </c>
@@ -12711,11 +12355,7 @@
         <v>95.947130000000001</v>
       </c>
     </row>
-    <row r="120" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H120">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="120" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J120">
         <v>1697.7449999999999</v>
       </c>
@@ -12723,11 +12363,7 @@
         <v>102.5564</v>
       </c>
     </row>
-    <row r="121" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H121">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="121" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J121">
         <v>1697.4570000000001</v>
       </c>
@@ -12735,11 +12371,7 @@
         <v>96.26979</v>
       </c>
     </row>
-    <row r="122" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H122">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="122" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J122">
         <v>1697.8979999999999</v>
       </c>
@@ -12747,11 +12379,7 @@
         <v>107.5222</v>
       </c>
     </row>
-    <row r="123" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H123">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="123" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J123">
         <v>1713.067</v>
       </c>
@@ -12759,11 +12387,7 @@
         <v>96.174220000000005</v>
       </c>
     </row>
-    <row r="124" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="124" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J124">
         <v>1713.4069999999999</v>
       </c>
@@ -12771,11 +12395,7 @@
         <v>111.3181</v>
       </c>
     </row>
-    <row r="125" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H125">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="125" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J125">
         <v>1713.269</v>
       </c>
@@ -12783,11 +12403,7 @@
         <v>96.214839999999995</v>
       </c>
     </row>
-    <row r="126" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H126">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="126" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J126">
         <v>1742.9939999999999</v>
       </c>
@@ -12795,11 +12411,7 @@
         <v>122.13800000000001</v>
       </c>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="127" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J127">
         <v>1773.7049999999999</v>
       </c>
@@ -12807,11 +12419,7 @@
         <v>105.7696</v>
       </c>
     </row>
-    <row r="128" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H128">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="128" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J128">
         <v>1788.712</v>
       </c>
@@ -12819,11 +12427,7 @@
         <v>106.3018</v>
       </c>
     </row>
-    <row r="129" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H129">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="129" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J129">
         <v>1803.973</v>
       </c>
@@ -12831,11 +12435,7 @@
         <v>106.0164</v>
       </c>
     </row>
-    <row r="130" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H130">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="130" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J130">
         <v>1803.799</v>
       </c>
@@ -12843,11 +12443,7 @@
         <v>106.0008</v>
       </c>
     </row>
-    <row r="131" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H131">
-        <f t="shared" ref="H131:H194" si="3">D131-F131</f>
-        <v>0</v>
-      </c>
+    <row r="131" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J131">
         <v>1788.7460000000001</v>
       </c>
@@ -12855,11 +12451,7 @@
         <v>106.2757</v>
       </c>
     </row>
-    <row r="132" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H132">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="132" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J132">
         <v>1803.846</v>
       </c>
@@ -12867,11 +12459,7 @@
         <v>105.7705</v>
       </c>
     </row>
-    <row r="133" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H133">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="133" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J133">
         <v>1788.356</v>
       </c>
@@ -12879,11 +12467,7 @@
         <v>106.0813</v>
       </c>
     </row>
-    <row r="134" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H134">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="134" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J134">
         <v>1773.8130000000001</v>
       </c>
@@ -12891,11 +12475,7 @@
         <v>106.3004</v>
       </c>
     </row>
-    <row r="135" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H135">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="135" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J135">
         <v>1773.46</v>
       </c>
@@ -12903,11 +12483,7 @@
         <v>105.8387</v>
       </c>
     </row>
-    <row r="136" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H136">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="136" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J136">
         <v>1773.855</v>
       </c>
@@ -12915,11 +12491,7 @@
         <v>106.3312</v>
       </c>
     </row>
-    <row r="137" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H137">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="137" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J137">
         <v>1758.252</v>
       </c>
@@ -12927,11 +12499,7 @@
         <v>105.94289999999999</v>
       </c>
     </row>
-    <row r="138" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H138">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="138" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J138">
         <v>1758.42</v>
       </c>
@@ -12939,11 +12507,7 @@
         <v>105.88379999999999</v>
       </c>
     </row>
-    <row r="139" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H139">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="139" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J139">
         <v>1743.6389999999999</v>
       </c>
@@ -12951,11 +12515,7 @@
         <v>105.9689</v>
       </c>
     </row>
-    <row r="140" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H140">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="140" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J140">
         <v>1743.116</v>
       </c>
@@ -12963,11 +12523,7 @@
         <v>106.07550000000001</v>
       </c>
     </row>
-    <row r="141" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H141">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="141" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J141">
         <v>1743.41</v>
       </c>
@@ -12975,11 +12531,7 @@
         <v>105.9944</v>
       </c>
     </row>
-    <row r="142" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H142">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="142" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J142">
         <v>1758.229</v>
       </c>
@@ -12987,11 +12539,7 @@
         <v>105.9682</v>
       </c>
     </row>
-    <row r="143" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H143">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="143" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J143">
         <v>1758.6110000000001</v>
       </c>
@@ -12999,11 +12547,7 @@
         <v>106.0844</v>
       </c>
     </row>
-    <row r="144" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H144">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="144" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J144">
         <v>1758.502</v>
       </c>
@@ -13011,11 +12555,7 @@
         <v>106.253</v>
       </c>
     </row>
-    <row r="145" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H145">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="145" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J145">
         <v>1758.336</v>
       </c>
@@ -13023,11 +12563,7 @@
         <v>105.9712</v>
       </c>
     </row>
-    <row r="146" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H146">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="146" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J146">
         <v>1743.46</v>
       </c>
@@ -13035,11 +12571,7 @@
         <v>105.7208</v>
       </c>
     </row>
-    <row r="147" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H147">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="147" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J147">
         <v>1743.7249999999999</v>
       </c>
@@ -13047,11 +12579,7 @@
         <v>106.00369999999999</v>
       </c>
     </row>
-    <row r="148" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H148">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="148" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J148">
         <v>1743.2550000000001</v>
       </c>
@@ -13059,11 +12587,7 @@
         <v>105.74850000000001</v>
       </c>
     </row>
-    <row r="149" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H149">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="149" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J149">
         <v>1743.2</v>
       </c>
@@ -13071,11 +12595,7 @@
         <v>105.6892</v>
       </c>
     </row>
-    <row r="150" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H150">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="150" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J150">
         <v>1743.645</v>
       </c>
@@ -13083,11 +12603,7 @@
         <v>115.9367</v>
       </c>
     </row>
-    <row r="151" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H151">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="151" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J151">
         <v>1743.6010000000001</v>
       </c>
@@ -13095,11 +12611,7 @@
         <v>115.7723</v>
       </c>
     </row>
-    <row r="152" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H152">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="152" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J152">
         <v>1743.2650000000001</v>
       </c>
@@ -13107,11 +12619,7 @@
         <v>115.5065</v>
       </c>
     </row>
-    <row r="153" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H153">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="153" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J153">
         <v>1743.1210000000001</v>
       </c>
@@ -13119,11 +12627,7 @@
         <v>116.05670000000001</v>
       </c>
     </row>
-    <row r="154" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H154">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="154" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J154">
         <v>1743.5830000000001</v>
       </c>
@@ -13131,11 +12635,7 @@
         <v>115.9269</v>
       </c>
     </row>
-    <row r="155" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H155">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="155" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J155">
         <v>1743.1949999999999</v>
       </c>
@@ -13143,11 +12643,7 @@
         <v>115.9965</v>
       </c>
     </row>
-    <row r="156" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H156">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="156" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J156">
         <v>1758.404</v>
       </c>
@@ -13155,11 +12651,7 @@
         <v>115.4991</v>
       </c>
     </row>
-    <row r="157" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="157" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J157">
         <v>1743.6780000000001</v>
       </c>
@@ -13167,11 +12659,7 @@
         <v>115.5228</v>
       </c>
     </row>
-    <row r="158" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H158">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="158" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J158">
         <v>1743.75</v>
       </c>
@@ -13179,11 +12667,7 @@
         <v>115.83710000000001</v>
       </c>
     </row>
-    <row r="159" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H159">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="159" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J159">
         <v>1743.4010000000001</v>
       </c>
@@ -13191,11 +12675,7 @@
         <v>115.67700000000001</v>
       </c>
     </row>
-    <row r="160" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H160">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="160" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J160">
         <v>1758.3130000000001</v>
       </c>
@@ -13203,11 +12683,7 @@
         <v>115.5472</v>
       </c>
     </row>
-    <row r="161" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H161">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="161" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J161">
         <v>1758.4659999999999</v>
       </c>
@@ -13215,11 +12691,7 @@
         <v>116.02809999999999</v>
       </c>
     </row>
-    <row r="162" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H162">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="162" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J162">
         <v>1758.309</v>
       </c>
@@ -13227,11 +12699,7 @@
         <v>115.7191</v>
       </c>
     </row>
-    <row r="163" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H163">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="163" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J163">
         <v>1758.383</v>
       </c>
@@ -13239,11 +12707,7 @@
         <v>115.8503</v>
       </c>
     </row>
-    <row r="164" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H164">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="164" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J164">
         <v>1758.7819999999999</v>
       </c>
@@ -13251,11 +12715,7 @@
         <v>116.01349999999999</v>
       </c>
     </row>
-    <row r="165" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H165">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="165" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J165">
         <v>1788.462</v>
       </c>
@@ -13263,11 +12723,7 @@
         <v>116.0718</v>
       </c>
     </row>
-    <row r="166" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H166">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="166" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J166">
         <v>1804.0540000000001</v>
       </c>
@@ -13275,11 +12731,7 @@
         <v>115.88200000000001</v>
       </c>
     </row>
-    <row r="167" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H167">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="167" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J167">
         <v>1804.001</v>
       </c>
@@ -13287,11 +12739,7 @@
         <v>115.82640000000001</v>
       </c>
     </row>
-    <row r="168" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H168">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="168" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J168">
         <v>1818.5730000000001</v>
       </c>
@@ -13299,11 +12747,7 @@
         <v>116.0414</v>
       </c>
     </row>
-    <row r="169" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H169">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="169" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J169">
         <v>1818.624</v>
       </c>
@@ -13311,11 +12755,7 @@
         <v>115.7786</v>
       </c>
     </row>
-    <row r="170" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H170">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="170" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J170">
         <v>1818.7860000000001</v>
       </c>
@@ -13323,11 +12763,7 @@
         <v>115.92440000000001</v>
       </c>
     </row>
-    <row r="171" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H171">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="171" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J171">
         <v>1834.075</v>
       </c>
@@ -13335,11 +12771,7 @@
         <v>116.0988</v>
       </c>
     </row>
-    <row r="172" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H172">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="172" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J172">
         <v>1834.6020000000001</v>
       </c>
@@ -13347,11 +12779,7 @@
         <v>115.9281</v>
       </c>
     </row>
-    <row r="173" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H173">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="173" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J173">
         <v>1834.0730000000001</v>
       </c>
@@ -13359,11 +12787,7 @@
         <v>115.8377</v>
       </c>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H174">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="174" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J174">
         <v>1834.4480000000001</v>
       </c>
@@ -13371,11 +12795,7 @@
         <v>116.0936</v>
       </c>
     </row>
-    <row r="175" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H175">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="175" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J175">
         <v>1834.4960000000001</v>
       </c>
@@ -13383,11 +12803,7 @@
         <v>115.8402</v>
       </c>
     </row>
-    <row r="176" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H176">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="176" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J176">
         <v>1849.4380000000001</v>
       </c>
@@ -13395,11 +12811,7 @@
         <v>116.17019999999999</v>
       </c>
     </row>
-    <row r="177" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H177">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="177" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J177">
         <v>1864.201</v>
       </c>
@@ -13407,11 +12819,7 @@
         <v>115.6253</v>
       </c>
     </row>
-    <row r="178" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H178">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="178" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J178">
         <v>1864.7149999999999</v>
       </c>
@@ -13419,11 +12827,7 @@
         <v>116.0719</v>
       </c>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H179">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="179" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J179">
         <v>1879.3689999999999</v>
       </c>
@@ -13431,11 +12835,7 @@
         <v>116.3058</v>
       </c>
     </row>
-    <row r="180" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H180">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="180" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J180">
         <v>1894.5129999999999</v>
       </c>
@@ -13443,11 +12843,7 @@
         <v>115.8853</v>
       </c>
     </row>
-    <row r="181" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H181">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="181" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J181">
         <v>1894.61</v>
       </c>
@@ -13455,11 +12851,7 @@
         <v>116.38339999999999</v>
       </c>
     </row>
-    <row r="182" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H182">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="182" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J182">
         <v>1895.0039999999999</v>
       </c>
@@ -13467,11 +12859,7 @@
         <v>116.1009</v>
       </c>
     </row>
-    <row r="183" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H183">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="183" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J183">
         <v>1909.9960000000001</v>
       </c>
@@ -13479,11 +12867,7 @@
         <v>126.40130000000001</v>
       </c>
     </row>
-    <row r="184" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H184">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="184" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J184">
         <v>1909.953</v>
       </c>
@@ -13491,11 +12875,7 @@
         <v>115.6763</v>
       </c>
     </row>
-    <row r="185" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H185">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="185" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J185">
         <v>1909.9480000000001</v>
       </c>
@@ -13503,11 +12883,7 @@
         <v>128.953</v>
       </c>
     </row>
-    <row r="186" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H186">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="186" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J186">
         <v>1925.124</v>
       </c>
@@ -13515,11 +12891,7 @@
         <v>115.9194</v>
       </c>
     </row>
-    <row r="187" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H187">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="187" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J187">
         <v>1924.905</v>
       </c>
@@ -13527,11 +12899,7 @@
         <v>131.6455</v>
       </c>
     </row>
-    <row r="188" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H188">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="188" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J188">
         <v>1939.692</v>
       </c>
@@ -13539,11 +12907,7 @@
         <v>115.86109999999999</v>
       </c>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H189">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="189" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J189">
         <v>1939.9169999999999</v>
       </c>
@@ -13551,11 +12915,7 @@
         <v>115.68819999999999</v>
       </c>
     </row>
-    <row r="190" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H190">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="190" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J190">
         <v>1955.596</v>
       </c>
@@ -13563,11 +12923,7 @@
         <v>116.19329999999999</v>
       </c>
     </row>
-    <row r="191" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H191">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="191" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J191">
         <v>1970.683</v>
       </c>
@@ -13575,11 +12931,7 @@
         <v>116.134</v>
       </c>
     </row>
-    <row r="192" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H192">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="192" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J192">
         <v>1970.617</v>
       </c>
@@ -13587,11 +12939,7 @@
         <v>116.1763</v>
       </c>
     </row>
-    <row r="193" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H193">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="193" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J193">
         <v>1970.1420000000001</v>
       </c>
@@ -13599,11 +12947,7 @@
         <v>116.0438</v>
       </c>
     </row>
-    <row r="194" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H194">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+    <row r="194" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J194">
         <v>1985.317</v>
       </c>
@@ -13611,11 +12955,7 @@
         <v>115.9259</v>
       </c>
     </row>
-    <row r="195" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H195">
-        <f t="shared" ref="H195:H258" si="4">D195-F195</f>
-        <v>0</v>
-      </c>
+    <row r="195" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J195">
         <v>1985.1020000000001</v>
       </c>
@@ -13623,11 +12963,7 @@
         <v>116.0008</v>
       </c>
     </row>
-    <row r="196" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H196">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="196" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J196">
         <v>2000.7739999999999</v>
       </c>
@@ -13635,11 +12971,7 @@
         <v>116.0121</v>
       </c>
     </row>
-    <row r="197" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H197">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="197" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J197">
         <v>2000.3019999999999</v>
       </c>
@@ -13647,11 +12979,7 @@
         <v>115.7264</v>
       </c>
     </row>
-    <row r="198" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H198">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="198" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J198">
         <v>2015.693</v>
       </c>
@@ -13659,11 +12987,7 @@
         <v>115.9374</v>
       </c>
     </row>
-    <row r="199" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H199">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="199" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J199">
         <v>2030.57</v>
       </c>
@@ -13671,11 +12995,7 @@
         <v>115.91459999999999</v>
       </c>
     </row>
-    <row r="200" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H200">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="200" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J200">
         <v>2046.1120000000001</v>
       </c>
@@ -13683,11 +13003,7 @@
         <v>115.63939999999999</v>
       </c>
     </row>
-    <row r="201" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H201">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="201" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J201">
         <v>2076.0819999999999</v>
       </c>
@@ -13695,11 +13011,7 @@
         <v>116.1581</v>
       </c>
     </row>
-    <row r="202" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H202">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="202" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J202">
         <v>2091.7159999999999</v>
       </c>
@@ -13707,11 +13019,7 @@
         <v>115.8416</v>
       </c>
     </row>
-    <row r="203" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H203">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="203" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J203">
         <v>2106.19</v>
       </c>
@@ -13719,11 +13027,7 @@
         <v>115.8566</v>
       </c>
     </row>
-    <row r="204" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H204">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="204" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J204">
         <v>2106.2840000000001</v>
       </c>
@@ -13731,11 +13035,7 @@
         <v>115.8509</v>
       </c>
     </row>
-    <row r="205" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H205">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="205" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J205">
         <v>2121.7220000000002</v>
       </c>
@@ -13743,11 +13043,7 @@
         <v>115.8514</v>
       </c>
     </row>
-    <row r="206" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H206">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="206" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J206">
         <v>2136.712</v>
       </c>
@@ -13755,11 +13051,7 @@
         <v>125.86709999999999</v>
       </c>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H207">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="207" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J207">
         <v>2136.752</v>
       </c>
@@ -13767,11 +13059,7 @@
         <v>125.4483</v>
       </c>
     </row>
-    <row r="208" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H208">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="208" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J208">
         <v>2136.913</v>
       </c>
@@ -13779,11 +13067,7 @@
         <v>125.4024</v>
       </c>
     </row>
-    <row r="209" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H209">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="209" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J209">
         <v>2167.261</v>
       </c>
@@ -13791,11 +13075,7 @@
         <v>125.7238</v>
       </c>
     </row>
-    <row r="210" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H210">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="210" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J210">
         <v>2181.7249999999999</v>
       </c>
@@ -13803,11 +13083,7 @@
         <v>125.682</v>
       </c>
     </row>
-    <row r="211" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H211">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="211" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J211">
         <v>2182.0329999999999</v>
       </c>
@@ -13815,11 +13091,7 @@
         <v>125.6857</v>
       </c>
     </row>
-    <row r="212" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H212">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="212" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J212">
         <v>2197.1640000000002</v>
       </c>
@@ -13827,11 +13099,7 @@
         <v>125.4738</v>
       </c>
     </row>
-    <row r="213" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H213">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="213" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J213">
         <v>2212.6770000000001</v>
       </c>
@@ -13839,11 +13107,7 @@
         <v>125.9331</v>
       </c>
     </row>
-    <row r="214" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H214">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="214" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J214">
         <v>2227.3980000000001</v>
       </c>
@@ -13851,11 +13115,7 @@
         <v>125.37139999999999</v>
       </c>
     </row>
-    <row r="215" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H215">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="215" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J215">
         <v>2242.422</v>
       </c>
@@ -13863,11 +13123,7 @@
         <v>125.9153</v>
       </c>
     </row>
-    <row r="216" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H216">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="216" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J216">
         <v>2257.8890000000001</v>
       </c>
@@ -13875,11 +13131,7 @@
         <v>125.6576</v>
       </c>
     </row>
-    <row r="217" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H217">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="217" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J217">
         <v>2272.59</v>
       </c>
@@ -13887,11 +13139,7 @@
         <v>125.5729</v>
       </c>
     </row>
-    <row r="218" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H218">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="218" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J218">
         <v>2288.2159999999999</v>
       </c>
@@ -13899,11 +13147,7 @@
         <v>125.9589</v>
       </c>
     </row>
-    <row r="219" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H219">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="219" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J219">
         <v>2302.7950000000001</v>
       </c>
@@ -13911,11 +13155,7 @@
         <v>135.2037</v>
       </c>
     </row>
-    <row r="220" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H220">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="220" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J220">
         <v>2318.6460000000002</v>
       </c>
@@ -13923,11 +13163,7 @@
         <v>135.52789999999999</v>
       </c>
     </row>
-    <row r="221" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H221">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="221" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J221">
         <v>2333.2890000000002</v>
       </c>
@@ -13935,11 +13171,7 @@
         <v>135.4736</v>
       </c>
     </row>
-    <row r="222" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H222">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="222" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J222">
         <v>2348.8989999999999</v>
       </c>
@@ -13947,11 +13179,7 @@
         <v>135.52209999999999</v>
       </c>
     </row>
-    <row r="223" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H223">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="223" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J223">
         <v>2363.453</v>
       </c>
@@ -13959,11 +13187,7 @@
         <v>135.203</v>
       </c>
     </row>
-    <row r="224" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H224">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="224" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J224">
         <v>2379.2429999999999</v>
       </c>
@@ -13971,11 +13195,7 @@
         <v>135.62870000000001</v>
       </c>
     </row>
-    <row r="225" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H225">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="225" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J225">
         <v>2378.7959999999998</v>
       </c>
@@ -13983,11 +13203,7 @@
         <v>135.7516</v>
       </c>
     </row>
-    <row r="226" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H226">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="226" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J226">
         <v>2379.1619999999998</v>
       </c>
@@ -13995,11 +13211,7 @@
         <v>135.196</v>
       </c>
     </row>
-    <row r="227" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="227" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J227">
         <v>2363.471</v>
       </c>
@@ -14007,11 +13219,7 @@
         <v>135.72149999999999</v>
       </c>
     </row>
-    <row r="228" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H228">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="228" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J228">
         <v>2318.3110000000001</v>
       </c>
@@ -14019,11 +13227,7 @@
         <v>135.15219999999999</v>
       </c>
     </row>
-    <row r="229" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H229">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="229" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J229">
         <v>2303.3679999999999</v>
       </c>
@@ -14031,11 +13235,7 @@
         <v>135.52850000000001</v>
       </c>
     </row>
-    <row r="230" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H230">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="230" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J230">
         <v>2303.4119999999998</v>
       </c>
@@ -14043,11 +13243,7 @@
         <v>135.50040000000001</v>
       </c>
     </row>
-    <row r="231" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H231">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="231" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J231">
         <v>2272.797</v>
       </c>
@@ -14055,11 +13251,7 @@
         <v>135.14279999999999</v>
       </c>
     </row>
-    <row r="232" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H232">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="232" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J232">
         <v>2257.855</v>
       </c>
@@ -14067,11 +13259,7 @@
         <v>135.7586</v>
       </c>
     </row>
-    <row r="233" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H233">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="233" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J233">
         <v>2257.732</v>
       </c>
@@ -14079,11 +13267,7 @@
         <v>135.2062</v>
       </c>
     </row>
-    <row r="234" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H234">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="234" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J234">
         <v>2243.0100000000002</v>
       </c>
@@ -14091,11 +13275,7 @@
         <v>135.19049999999999</v>
       </c>
     </row>
-    <row r="235" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H235">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="235" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J235">
         <v>2227.8380000000002</v>
       </c>
@@ -14103,11 +13283,7 @@
         <v>135.5018</v>
       </c>
     </row>
-    <row r="236" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H236">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="236" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J236">
         <v>2227.8609999999999</v>
       </c>
@@ -14115,11 +13291,7 @@
         <v>135.70230000000001</v>
       </c>
     </row>
-    <row r="237" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H237">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="237" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J237">
         <v>2227.7280000000001</v>
       </c>
@@ -14127,11 +13299,7 @@
         <v>135.14320000000001</v>
       </c>
     </row>
-    <row r="238" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H238">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="238" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J238">
         <v>2212.5929999999998</v>
       </c>
@@ -14139,11 +13307,7 @@
         <v>135.9186</v>
       </c>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H239">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="239" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J239">
         <v>2212.4630000000002</v>
       </c>
@@ -14151,11 +13315,7 @@
         <v>135.1687</v>
       </c>
     </row>
-    <row r="240" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H240">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="240" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J240">
         <v>2197.69</v>
       </c>
@@ -14163,11 +13323,7 @@
         <v>136.13910000000001</v>
       </c>
     </row>
-    <row r="241" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H241">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="241" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J241">
         <v>2197.442</v>
       </c>
@@ -14175,11 +13331,7 @@
         <v>135.43340000000001</v>
       </c>
     </row>
-    <row r="242" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H242">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="242" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J242">
         <v>2197.8220000000001</v>
       </c>
@@ -14187,11 +13339,7 @@
         <v>146.0427</v>
       </c>
     </row>
-    <row r="243" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H243">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="243" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J243">
         <v>2181.6410000000001</v>
       </c>
@@ -14199,11 +13347,7 @@
         <v>135.41380000000001</v>
       </c>
     </row>
-    <row r="244" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H244">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="244" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J244">
         <v>2181.77</v>
       </c>
@@ -14211,11 +13355,7 @@
         <v>148.27549999999999</v>
       </c>
     </row>
-    <row r="245" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H245">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="245" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J245">
         <v>2182.2109999999998</v>
       </c>
@@ -14223,11 +13363,7 @@
         <v>135.7269</v>
       </c>
     </row>
-    <row r="246" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H246">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="246" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J246">
         <v>2166.9209999999998</v>
       </c>
@@ -14235,11 +13371,7 @@
         <v>150.4016</v>
       </c>
     </row>
-    <row r="247" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H247">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="247" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J247">
         <v>2167.4630000000002</v>
       </c>
@@ -14247,11 +13379,7 @@
         <v>135.68629999999999</v>
       </c>
     </row>
-    <row r="248" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H248">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="248" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J248">
         <v>2166.9349999999999</v>
       </c>
@@ -14259,11 +13387,7 @@
         <v>149.3246</v>
       </c>
     </row>
-    <row r="249" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H249">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="249" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J249">
         <v>2152.0659999999998</v>
       </c>
@@ -14271,11 +13395,7 @@
         <v>135.16829999999999</v>
       </c>
     </row>
-    <row r="250" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H250">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="250" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J250">
         <v>2151.8969999999999</v>
       </c>
@@ -14283,11 +13403,7 @@
         <v>135.63730000000001</v>
       </c>
     </row>
-    <row r="251" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H251">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="251" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J251">
         <v>2151.701</v>
       </c>
@@ -14295,11 +13411,7 @@
         <v>135.42089999999999</v>
       </c>
     </row>
-    <row r="252" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H252">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="252" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J252">
         <v>2152.1179999999999</v>
       </c>
@@ -14307,11 +13419,7 @@
         <v>135.44110000000001</v>
       </c>
     </row>
-    <row r="253" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H253">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="253" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J253">
         <v>2137.1120000000001</v>
       </c>
@@ -14319,11 +13427,7 @@
         <v>135.73140000000001</v>
       </c>
     </row>
-    <row r="254" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H254">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="254" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J254">
         <v>2152.1480000000001</v>
       </c>
@@ -14331,11 +13435,7 @@
         <v>135.52979999999999</v>
       </c>
     </row>
-    <row r="255" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H255">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="255" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J255">
         <v>2136.7139999999999</v>
       </c>
@@ -14343,11 +13443,7 @@
         <v>135.16589999999999</v>
       </c>
     </row>
-    <row r="256" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H256">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="256" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J256">
         <v>2136.7220000000002</v>
       </c>
@@ -14355,11 +13451,7 @@
         <v>135.43109999999999</v>
       </c>
     </row>
-    <row r="257" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H257">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="257" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J257">
         <v>2137.1190000000001</v>
       </c>
@@ -14367,11 +13459,7 @@
         <v>135.6944</v>
       </c>
     </row>
-    <row r="258" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H258">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+    <row r="258" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J258">
         <v>2137.2060000000001</v>
       </c>
@@ -14379,11 +13467,7 @@
         <v>135.5111</v>
       </c>
     </row>
-    <row r="259" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H259">
-        <f t="shared" ref="H259:H297" si="5">D259-F259</f>
-        <v>0</v>
-      </c>
+    <row r="259" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J259">
         <v>2137.136</v>
       </c>
@@ -14391,11 +13475,7 @@
         <v>135.74529999999999</v>
       </c>
     </row>
-    <row r="260" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H260">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="260" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J260">
         <v>2136.998</v>
       </c>
@@ -14403,11 +13483,7 @@
         <v>135.589</v>
       </c>
     </row>
-    <row r="261" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H261">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="261" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J261">
         <v>2137.0430000000001</v>
       </c>
@@ -14415,11 +13491,7 @@
         <v>135.4787</v>
       </c>
     </row>
-    <row r="262" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H262">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="262" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J262">
         <v>2136.9940000000001</v>
       </c>
@@ -14427,11 +13499,7 @@
         <v>135.501</v>
       </c>
     </row>
-    <row r="263" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H263">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="263" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J263">
         <v>2151.7600000000002</v>
       </c>
@@ -14439,11 +13507,7 @@
         <v>135.68340000000001</v>
       </c>
     </row>
-    <row r="264" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H264">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="264" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J264">
         <v>2136.674</v>
       </c>
@@ -14451,11 +13515,7 @@
         <v>135.40479999999999</v>
       </c>
     </row>
-    <row r="265" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H265">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="265" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J265">
         <v>2151.973</v>
       </c>
@@ -14463,11 +13523,7 @@
         <v>135.34440000000001</v>
       </c>
     </row>
-    <row r="266" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H266">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="266" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J266">
         <v>2151.9319999999998</v>
       </c>
@@ -14475,11 +13531,7 @@
         <v>135.4581</v>
       </c>
     </row>
-    <row r="267" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H267">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="267" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J267">
         <v>2151.9209999999998</v>
       </c>
@@ -14487,11 +13539,7 @@
         <v>135.1977</v>
       </c>
     </row>
-    <row r="268" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H268">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="268" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J268">
         <v>2151.9989999999998</v>
       </c>
@@ -14499,11 +13547,7 @@
         <v>135.34399999999999</v>
       </c>
     </row>
-    <row r="269" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H269">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="269" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J269">
         <v>2166.6460000000002</v>
       </c>
@@ -14511,11 +13555,7 @@
         <v>135.76349999999999</v>
       </c>
     </row>
-    <row r="270" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H270">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="270" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J270">
         <v>2152.134</v>
       </c>
@@ -14523,11 +13563,7 @@
         <v>135.49199999999999</v>
       </c>
     </row>
-    <row r="271" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H271">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="271" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J271">
         <v>2167.125</v>
       </c>
@@ -14535,11 +13571,7 @@
         <v>135.47919999999999</v>
       </c>
     </row>
-    <row r="272" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H272">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="272" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J272">
         <v>2166.8739999999998</v>
       </c>
@@ -14547,11 +13579,7 @@
         <v>135.7834</v>
       </c>
     </row>
-    <row r="273" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H273">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="273" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J273">
         <v>2182.17</v>
       </c>
@@ -14559,11 +13587,7 @@
         <v>135.50450000000001</v>
       </c>
     </row>
-    <row r="274" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H274">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="274" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J274">
         <v>2182.067</v>
       </c>
@@ -14571,11 +13595,7 @@
         <v>135.22200000000001</v>
       </c>
     </row>
-    <row r="275" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H275">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="275" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J275">
         <v>2197.5309999999999</v>
       </c>
@@ -14583,11 +13603,7 @@
         <v>135.49209999999999</v>
       </c>
     </row>
-    <row r="276" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H276">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="276" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J276">
         <v>2197.299</v>
       </c>
@@ -14595,11 +13611,7 @@
         <v>135.19800000000001</v>
       </c>
     </row>
-    <row r="277" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H277">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="277" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J277">
         <v>2212.5549999999998</v>
       </c>
@@ -14607,11 +13619,7 @@
         <v>135.47669999999999</v>
       </c>
     </row>
-    <row r="278" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="278" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J278">
         <v>2227.5909999999999</v>
       </c>
@@ -14619,11 +13627,7 @@
         <v>135.24359999999999</v>
       </c>
     </row>
-    <row r="279" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H279">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="279" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J279">
         <v>2242.674</v>
       </c>
@@ -14631,11 +13635,7 @@
         <v>135.78200000000001</v>
       </c>
     </row>
-    <row r="280" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H280">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="280" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J280">
         <v>2242.6320000000001</v>
       </c>
@@ -14643,11 +13643,7 @@
         <v>135.61869999999999</v>
       </c>
     </row>
-    <row r="281" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H281">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="281" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J281">
         <v>2257.8119999999999</v>
       </c>
@@ -14655,11 +13651,7 @@
         <v>135.5112</v>
       </c>
     </row>
-    <row r="282" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H282">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="282" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J282">
         <v>2257.9879999999998</v>
       </c>
@@ -14667,11 +13659,7 @@
         <v>135.25960000000001</v>
       </c>
     </row>
-    <row r="283" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H283">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="283" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J283">
         <v>2273.31</v>
       </c>
@@ -14679,11 +13667,7 @@
         <v>135.57429999999999</v>
       </c>
     </row>
-    <row r="284" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H284">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="284" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J284">
         <v>2272.7620000000002</v>
       </c>
@@ -14691,11 +13675,7 @@
         <v>135.48140000000001</v>
       </c>
     </row>
-    <row r="285" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H285">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="285" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J285">
         <v>2272.7910000000002</v>
       </c>
@@ -14703,11 +13683,7 @@
         <v>135.24860000000001</v>
       </c>
     </row>
-    <row r="286" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H286">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="286" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J286">
         <v>2303.0889999999999</v>
       </c>
@@ -14715,11 +13691,7 @@
         <v>135.2543</v>
       </c>
     </row>
-    <row r="287" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H287">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="287" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J287">
         <v>2318.8209999999999</v>
       </c>
@@ -14727,11 +13699,7 @@
         <v>135.78460000000001</v>
       </c>
     </row>
-    <row r="288" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H288">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="288" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J288">
         <v>2334.0030000000002</v>
       </c>
@@ -14739,11 +13707,7 @@
         <v>135.56190000000001</v>
       </c>
     </row>
-    <row r="289" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H289">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="289" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J289">
         <v>2348.922</v>
       </c>
@@ -14751,11 +13715,7 @@
         <v>135.61609999999999</v>
       </c>
     </row>
-    <row r="290" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H290">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="290" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J290">
         <v>2348.8249999999998</v>
       </c>
@@ -14763,11 +13723,7 @@
         <v>135.52010000000001</v>
       </c>
     </row>
-    <row r="291" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H291">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="291" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J291">
         <v>2348.7159999999999</v>
       </c>
@@ -14775,11 +13731,7 @@
         <v>135.76300000000001</v>
       </c>
     </row>
-    <row r="292" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H292">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="292" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J292">
         <v>2363.6129999999998</v>
       </c>
@@ -14787,11 +13739,7 @@
         <v>135.53290000000001</v>
       </c>
     </row>
-    <row r="293" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H293">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="293" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J293">
         <v>2378.8510000000001</v>
       </c>
@@ -14799,11 +13747,7 @@
         <v>135.28210000000001</v>
       </c>
     </row>
-    <row r="294" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H294">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="294" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J294">
         <v>2379.19</v>
       </c>
@@ -14811,11 +13755,7 @@
         <v>135.48609999999999</v>
       </c>
     </row>
-    <row r="295" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H295">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="295" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J295">
         <v>2394.2730000000001</v>
       </c>
@@ -14823,11 +13763,7 @@
         <v>135.55950000000001</v>
       </c>
     </row>
-    <row r="296" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H296">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="296" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J296">
         <v>2393.9299999999998</v>
       </c>
@@ -14835,11 +13771,7 @@
         <v>135.2533</v>
       </c>
     </row>
-    <row r="297" spans="8:11" x14ac:dyDescent="0.75">
-      <c r="H297">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="297" spans="10:11" x14ac:dyDescent="0.75">
       <c r="J297">
         <v>2394.2550000000001</v>
       </c>
@@ -14854,6 +13786,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0ed78115-f4df-42b0-9376-ad3306022cc8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100205AA101E2883C419D53A6EAA58BE6E4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0732453c88b6c24a50b901808cd2a95">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0ed78115-f4df-42b0-9376-ad3306022cc8" xmlns:ns4="94b7f148-c09a-42e6-baca-973a9a7cd962" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c3ce456d5e9a668ce7bebc57d13ab49" ns3:_="" ns4:_="">
     <xsd:import namespace="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
@@ -15106,24 +14055,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0ed78115-f4df-42b0-9376-ad3306022cc8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3CDB75-004F-4418-A9D1-0A5E1B428212}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="94b7f148-c09a-42e6-baca-973a9a7cd962"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D38091-7891-4922-BDA4-DDCC3109030A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88B5DFD5-AF32-4053-8117-B9F97580063E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15140,29 +14097,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3CDB75-004F-4418-A9D1-0A5E1B428212}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="94b7f148-c09a-42e6-baca-973a9a7cd962"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D38091-7891-4922-BDA4-DDCC3109030A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/01_Raw_data/RC log.xlsx
+++ b/01_Raw_data/RC log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71870B2-B66D-4B38-8E47-642B227FC755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40177EE-A074-4ED3-94CC-D63DF641D6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2220" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A079E74B-2391-4069-81A1-6515CCD90540}"/>
+    <workbookView xWindow="-20100" yWindow="5745" windowWidth="14400" windowHeight="12165" xr2:uid="{A079E74B-2391-4069-81A1-6515CCD90540}"/>
   </bookViews>
   <sheets>
     <sheet name="RC log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -2829,6 +2829,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2836,7 +2837,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3837,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04E7760-F87C-4D84-A63F-D473D279D553}">
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="9.40625" bestFit="1" customWidth="1"/>
@@ -6894,6 +6894,9 @@
       <c r="E104">
         <v>0</v>
       </c>
+      <c r="K104">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A105" s="1">
@@ -9392,7 +9395,7 @@
         <v>0.39</v>
       </c>
       <c r="G189">
-        <f t="shared" ref="G189:G214" si="8">E189-F189</f>
+        <f t="shared" ref="G189:G231" si="8">E189-F189</f>
         <v>-0.21000000000000002</v>
       </c>
       <c r="H189">
@@ -9681,6 +9684,9 @@
       <c r="D199" t="s">
         <v>6</v>
       </c>
+      <c r="K199">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A200" s="1">
@@ -10144,6 +10150,483 @@
       </c>
       <c r="D215" t="s">
         <v>37</v>
+      </c>
+      <c r="K215">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A216" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B216">
+        <v>5</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="s">
+        <v>6</v>
+      </c>
+      <c r="E216">
+        <v>0.44</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216">
+        <f t="shared" si="8"/>
+        <v>-0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A217" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B217">
+        <v>5</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="D217" t="s">
+        <v>7</v>
+      </c>
+      <c r="E217">
+        <v>0.39</v>
+      </c>
+      <c r="F217">
+        <v>0.78</v>
+      </c>
+      <c r="G217">
+        <f t="shared" si="8"/>
+        <v>-0.39</v>
+      </c>
+      <c r="H217">
+        <v>6.22</v>
+      </c>
+      <c r="K217">
+        <v>15.22</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A218" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B218">
+        <v>5</v>
+      </c>
+      <c r="C218">
+        <v>3</v>
+      </c>
+      <c r="D218" t="s">
+        <v>8</v>
+      </c>
+      <c r="E218">
+        <v>0.755</v>
+      </c>
+      <c r="F218">
+        <v>1.04</v>
+      </c>
+      <c r="G218">
+        <f t="shared" si="8"/>
+        <v>-0.28500000000000003</v>
+      </c>
+      <c r="H218">
+        <v>6.1</v>
+      </c>
+      <c r="K218">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A219" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B219">
+        <v>5</v>
+      </c>
+      <c r="C219">
+        <v>4</v>
+      </c>
+      <c r="D219" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219">
+        <v>0.21</v>
+      </c>
+      <c r="F219">
+        <v>1.08</v>
+      </c>
+      <c r="G219">
+        <f t="shared" si="8"/>
+        <v>-0.87000000000000011</v>
+      </c>
+      <c r="H219">
+        <v>5.16</v>
+      </c>
+      <c r="K219">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A220" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B220">
+        <v>5</v>
+      </c>
+      <c r="C220">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>10</v>
+      </c>
+      <c r="E220">
+        <v>0.09</v>
+      </c>
+      <c r="F220">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G220">
+        <f t="shared" si="8"/>
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="H220">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="K220">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A221" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B221">
+        <v>5</v>
+      </c>
+      <c r="C221">
+        <v>6</v>
+      </c>
+      <c r="D221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221">
+        <v>0.04</v>
+      </c>
+      <c r="F221">
+        <v>0.82</v>
+      </c>
+      <c r="G221">
+        <f t="shared" si="8"/>
+        <v>-0.77999999999999992</v>
+      </c>
+      <c r="H221">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="K221">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A222" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B222">
+        <v>5</v>
+      </c>
+      <c r="C222">
+        <v>8</v>
+      </c>
+      <c r="D222" t="s">
+        <v>36</v>
+      </c>
+      <c r="E222">
+        <v>0.83</v>
+      </c>
+      <c r="F222">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="G222">
+        <f t="shared" si="8"/>
+        <v>-0.28000000000000014</v>
+      </c>
+      <c r="H222">
+        <v>5.82</v>
+      </c>
+      <c r="K222">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A223" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B223">
+        <v>6</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>14</v>
+      </c>
+      <c r="E223">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F223">
+        <v>1.41</v>
+      </c>
+      <c r="G223">
+        <f t="shared" si="8"/>
+        <v>-1.27</v>
+      </c>
+      <c r="H223">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K223">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A224" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B224">
+        <v>6</v>
+      </c>
+      <c r="C224">
+        <v>2</v>
+      </c>
+      <c r="D224" t="s">
+        <v>15</v>
+      </c>
+      <c r="E224">
+        <v>0.79</v>
+      </c>
+      <c r="F224">
+        <v>1.83</v>
+      </c>
+      <c r="G224">
+        <f t="shared" si="8"/>
+        <v>-1.04</v>
+      </c>
+      <c r="H224">
+        <v>4.45</v>
+      </c>
+      <c r="K224">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A225" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B225">
+        <v>6</v>
+      </c>
+      <c r="C225">
+        <v>3</v>
+      </c>
+      <c r="D225" t="s">
+        <v>16</v>
+      </c>
+      <c r="E225">
+        <v>0.02</v>
+      </c>
+      <c r="F225">
+        <v>1.03</v>
+      </c>
+      <c r="G225">
+        <f t="shared" si="8"/>
+        <v>-1.01</v>
+      </c>
+      <c r="H225">
+        <v>5.21</v>
+      </c>
+      <c r="K225">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A226" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B226">
+        <v>6</v>
+      </c>
+      <c r="C226">
+        <v>4</v>
+      </c>
+      <c r="D226" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226">
+        <v>0.2</v>
+      </c>
+      <c r="F226">
+        <v>0.66</v>
+      </c>
+      <c r="G226">
+        <f t="shared" si="8"/>
+        <v>-0.46</v>
+      </c>
+      <c r="H226">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K226">
+        <v>17.010000000000002</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A227" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B227">
+        <v>9</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227">
+        <v>0.27</v>
+      </c>
+      <c r="F227">
+        <v>0.61</v>
+      </c>
+      <c r="G227">
+        <f t="shared" si="8"/>
+        <v>-0.33999999999999997</v>
+      </c>
+      <c r="H227">
+        <v>4.37</v>
+      </c>
+      <c r="K227">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A228" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B228">
+        <v>9</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+      <c r="D228" t="s">
+        <v>20</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>0.65</v>
+      </c>
+      <c r="G228">
+        <f t="shared" si="8"/>
+        <v>-0.65</v>
+      </c>
+      <c r="H228">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="K228">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A229" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B229">
+        <v>9</v>
+      </c>
+      <c r="C229">
+        <v>3</v>
+      </c>
+      <c r="D229" t="s">
+        <v>21</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>0.84</v>
+      </c>
+      <c r="G229">
+        <f t="shared" si="8"/>
+        <v>-0.84</v>
+      </c>
+      <c r="H229">
+        <v>3.81</v>
+      </c>
+      <c r="K229">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A230" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B230">
+        <v>9</v>
+      </c>
+      <c r="C230">
+        <v>4</v>
+      </c>
+      <c r="D230" t="s">
+        <v>22</v>
+      </c>
+      <c r="E230">
+        <v>0.31</v>
+      </c>
+      <c r="F230">
+        <v>1.4</v>
+      </c>
+      <c r="G230">
+        <f t="shared" si="8"/>
+        <v>-1.0899999999999999</v>
+      </c>
+      <c r="H230">
+        <v>4.08</v>
+      </c>
+      <c r="K230">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
+      <c r="A231" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B231">
+        <v>9</v>
+      </c>
+      <c r="C231">
+        <v>5</v>
+      </c>
+      <c r="D231" t="s">
+        <v>37</v>
+      </c>
+      <c r="E231">
+        <v>0.03</v>
+      </c>
+      <c r="F231">
+        <v>1.47</v>
+      </c>
+      <c r="G231">
+        <f t="shared" si="8"/>
+        <v>-1.44</v>
+      </c>
+      <c r="H231">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="K231">
+        <v>17.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -13786,23 +14269,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0ed78115-f4df-42b0-9376-ad3306022cc8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100205AA101E2883C419D53A6EAA58BE6E4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0732453c88b6c24a50b901808cd2a95">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0ed78115-f4df-42b0-9376-ad3306022cc8" xmlns:ns4="94b7f148-c09a-42e6-baca-973a9a7cd962" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c3ce456d5e9a668ce7bebc57d13ab49" ns3:_="" ns4:_="">
     <xsd:import namespace="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
@@ -14055,32 +14521,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3CDB75-004F-4418-A9D1-0A5E1B428212}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="94b7f148-c09a-42e6-baca-973a9a7cd962"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D38091-7891-4922-BDA4-DDCC3109030A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0ed78115-f4df-42b0-9376-ad3306022cc8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88B5DFD5-AF32-4053-8117-B9F97580063E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14097,4 +14555,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D38091-7891-4922-BDA4-DDCC3109030A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3CDB75-004F-4418-A9D1-0A5E1B428212}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="0ed78115-f4df-42b0-9376-ad3306022cc8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="94b7f148-c09a-42e6-baca-973a9a7cd962"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>